--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62288.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62288.xlsx
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62288.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62288.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Name nom</t>
         </is>
       </c>
     </row>
